--- a/turnos/plan.xlsx
+++ b/turnos/plan.xlsx
@@ -2042,10 +2042,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2058,9 +2061,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2470,6 +2470,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AI448"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="11.1" customHeight="1"/>
   <cols>
@@ -2582,11 +2585,11 @@
       <c r="N2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O2" s="230" t="s">
+      <c r="O2" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="230"/>
-      <c r="Q2" s="230"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
       <c r="R2" s="14" t="s">
         <v>16</v>
       </c>
@@ -4157,11 +4160,11 @@
       <c r="N35" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O35" s="230" t="s">
+      <c r="O35" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P35" s="230"/>
-      <c r="Q35" s="230"/>
+      <c r="P35" s="232"/>
+      <c r="Q35" s="232"/>
       <c r="R35" s="14" t="s">
         <v>16</v>
       </c>
@@ -5556,18 +5559,18 @@
       <c r="D65" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E65" s="233" t="s">
+      <c r="E65" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="F65" s="234"/>
-      <c r="G65" s="234"/>
-      <c r="H65" s="234"/>
-      <c r="I65" s="234"/>
-      <c r="J65" s="234"/>
-      <c r="K65" s="234"/>
-      <c r="L65" s="234"/>
-      <c r="M65" s="234"/>
-      <c r="N65" s="235"/>
+      <c r="F65" s="235"/>
+      <c r="G65" s="235"/>
+      <c r="H65" s="235"/>
+      <c r="I65" s="235"/>
+      <c r="J65" s="235"/>
+      <c r="K65" s="235"/>
+      <c r="L65" s="235"/>
+      <c r="M65" s="235"/>
+      <c r="N65" s="236"/>
       <c r="O65" s="229" t="s">
         <v>3</v>
       </c>
@@ -5633,11 +5636,11 @@
       <c r="N66" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O66" s="230" t="s">
+      <c r="O66" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P66" s="230"/>
-      <c r="Q66" s="230"/>
+      <c r="P66" s="232"/>
+      <c r="Q66" s="232"/>
       <c r="R66" s="14" t="s">
         <v>16</v>
       </c>
@@ -7110,35 +7113,35 @@
       <c r="D98" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="E98" s="236" t="s">
+      <c r="E98" s="231" t="s">
         <v>2</v>
       </c>
-      <c r="F98" s="236"/>
-      <c r="G98" s="236"/>
-      <c r="H98" s="236"/>
-      <c r="I98" s="236"/>
-      <c r="J98" s="236"/>
-      <c r="K98" s="236"/>
-      <c r="L98" s="236"/>
-      <c r="M98" s="236"/>
-      <c r="N98" s="236"/>
-      <c r="O98" s="236" t="s">
+      <c r="F98" s="231"/>
+      <c r="G98" s="231"/>
+      <c r="H98" s="231"/>
+      <c r="I98" s="231"/>
+      <c r="J98" s="231"/>
+      <c r="K98" s="231"/>
+      <c r="L98" s="231"/>
+      <c r="M98" s="231"/>
+      <c r="N98" s="231"/>
+      <c r="O98" s="231" t="s">
         <v>3</v>
       </c>
-      <c r="P98" s="236"/>
-      <c r="Q98" s="236"/>
-      <c r="R98" s="236"/>
+      <c r="P98" s="231"/>
+      <c r="Q98" s="231"/>
+      <c r="R98" s="231"/>
       <c r="S98" s="77" t="s">
         <v>4</v>
       </c>
       <c r="T98" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="U98" s="236" t="s">
+      <c r="U98" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="V98" s="236"/>
-      <c r="W98" s="236"/>
+      <c r="V98" s="231"/>
+      <c r="W98" s="231"/>
       <c r="X98" s="203" t="s">
         <v>74</v>
       </c>
@@ -7187,11 +7190,11 @@
       <c r="N99" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="O99" s="232" t="s">
+      <c r="O99" s="233" t="s">
         <v>15</v>
       </c>
-      <c r="P99" s="232"/>
-      <c r="Q99" s="232"/>
+      <c r="P99" s="233"/>
+      <c r="Q99" s="233"/>
       <c r="R99" s="14" t="s">
         <v>16</v>
       </c>
@@ -8713,35 +8716,35 @@
       <c r="D130" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="E130" s="231" t="s">
+      <c r="E130" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="F130" s="231"/>
-      <c r="G130" s="231"/>
-      <c r="H130" s="231"/>
-      <c r="I130" s="231"/>
-      <c r="J130" s="231"/>
-      <c r="K130" s="231"/>
-      <c r="L130" s="231"/>
-      <c r="M130" s="231"/>
-      <c r="N130" s="231"/>
-      <c r="O130" s="231" t="s">
+      <c r="F130" s="230"/>
+      <c r="G130" s="230"/>
+      <c r="H130" s="230"/>
+      <c r="I130" s="230"/>
+      <c r="J130" s="230"/>
+      <c r="K130" s="230"/>
+      <c r="L130" s="230"/>
+      <c r="M130" s="230"/>
+      <c r="N130" s="230"/>
+      <c r="O130" s="230" t="s">
         <v>3</v>
       </c>
-      <c r="P130" s="231"/>
-      <c r="Q130" s="231"/>
-      <c r="R130" s="231"/>
+      <c r="P130" s="230"/>
+      <c r="Q130" s="230"/>
+      <c r="R130" s="230"/>
       <c r="S130" s="79" t="s">
         <v>4</v>
       </c>
       <c r="T130" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="U130" s="231" t="s">
+      <c r="U130" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="V130" s="231"/>
-      <c r="W130" s="231"/>
+      <c r="V130" s="230"/>
+      <c r="W130" s="230"/>
       <c r="X130" s="204" t="s">
         <v>7</v>
       </c>
@@ -8792,11 +8795,11 @@
       <c r="N131" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O131" s="230" t="s">
+      <c r="O131" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P131" s="230"/>
-      <c r="Q131" s="230"/>
+      <c r="P131" s="232"/>
+      <c r="Q131" s="232"/>
       <c r="R131" s="14" t="s">
         <v>16</v>
       </c>
@@ -10455,11 +10458,11 @@
       <c r="N164" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O164" s="230" t="s">
+      <c r="O164" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P164" s="230"/>
-      <c r="Q164" s="230"/>
+      <c r="P164" s="232"/>
+      <c r="Q164" s="232"/>
       <c r="R164" s="14" t="s">
         <v>16</v>
       </c>
@@ -12120,11 +12123,11 @@
       <c r="N196" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O196" s="230" t="s">
+      <c r="O196" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P196" s="230"/>
-      <c r="Q196" s="230"/>
+      <c r="P196" s="232"/>
+      <c r="Q196" s="232"/>
       <c r="R196" s="14" t="s">
         <v>16</v>
       </c>
@@ -13625,11 +13628,11 @@
       <c r="N228" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O228" s="230" t="s">
+      <c r="O228" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P228" s="230"/>
-      <c r="Q228" s="230"/>
+      <c r="P228" s="232"/>
+      <c r="Q228" s="232"/>
       <c r="R228" s="14" t="s">
         <v>16</v>
       </c>
@@ -13668,9 +13671,9 @@
       <c r="L229" s="101"/>
       <c r="M229" s="16"/>
       <c r="N229" s="16"/>
-      <c r="O229" s="230"/>
-      <c r="P229" s="230"/>
-      <c r="Q229" s="230"/>
+      <c r="O229" s="232"/>
+      <c r="P229" s="232"/>
+      <c r="Q229" s="232"/>
       <c r="R229" s="14"/>
       <c r="S229" s="46"/>
       <c r="T229" s="46"/>
@@ -15241,11 +15244,11 @@
       <c r="N262" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O262" s="230" t="s">
+      <c r="O262" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P262" s="230"/>
-      <c r="Q262" s="230"/>
+      <c r="P262" s="232"/>
+      <c r="Q262" s="232"/>
       <c r="R262" s="14" t="s">
         <v>16</v>
       </c>
@@ -16727,11 +16730,11 @@
       <c r="N294" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O294" s="230" t="s">
+      <c r="O294" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P294" s="230"/>
-      <c r="Q294" s="230"/>
+      <c r="P294" s="232"/>
+      <c r="Q294" s="232"/>
       <c r="R294" s="14" t="s">
         <v>16</v>
       </c>
@@ -17950,7 +17953,7 @@
         <v>4</v>
       </c>
       <c r="D321" s="25" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="E321" s="25"/>
       <c r="F321" s="25"/>
@@ -18282,11 +18285,11 @@
       <c r="N327" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O327" s="230" t="s">
+      <c r="O327" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P327" s="230"/>
-      <c r="Q327" s="230"/>
+      <c r="P327" s="232"/>
+      <c r="Q327" s="232"/>
       <c r="R327" s="14" t="s">
         <v>16</v>
       </c>
@@ -18516,9 +18519,7 @@
       <c r="E332" s="25"/>
       <c r="F332" s="25"/>
       <c r="G332" s="25"/>
-      <c r="H332" s="25" t="s">
-        <v>11</v>
-      </c>
+      <c r="H332" s="25"/>
       <c r="I332" s="25"/>
       <c r="J332" s="25"/>
       <c r="K332" s="39"/>
@@ -18724,7 +18725,7 @@
       <c r="Q336" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="R336" s="25"/>
+      <c r="R336" s="185"/>
       <c r="S336" s="25" t="s">
         <v>260</v>
       </c>
@@ -19121,7 +19122,7 @@
       <c r="Q344" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="R344" s="25"/>
+      <c r="R344" s="185"/>
       <c r="S344" s="25"/>
       <c r="T344" s="25"/>
       <c r="U344" s="25"/>
@@ -19414,7 +19415,7 @@
       <c r="Q350" s="139" t="s">
         <v>294</v>
       </c>
-      <c r="R350" s="25"/>
+      <c r="R350" s="185"/>
       <c r="S350" s="25" t="s">
         <v>146</v>
       </c>
@@ -19855,11 +19856,11 @@
       <c r="N359" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O359" s="230" t="s">
+      <c r="O359" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P359" s="230"/>
-      <c r="Q359" s="230"/>
+      <c r="P359" s="232"/>
+      <c r="Q359" s="232"/>
       <c r="R359" s="14" t="s">
         <v>16</v>
       </c>
@@ -20283,9 +20284,11 @@
         <v>11</v>
       </c>
       <c r="P368" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q368" s="45"/>
+        <v>18</v>
+      </c>
+      <c r="Q368" s="45" t="s">
+        <v>15</v>
+      </c>
       <c r="R368" s="25"/>
       <c r="S368" s="25"/>
       <c r="T368" s="56"/>
@@ -21363,11 +21366,11 @@
       <c r="N392" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O392" s="230" t="s">
+      <c r="O392" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P392" s="230"/>
-      <c r="Q392" s="230"/>
+      <c r="P392" s="232"/>
+      <c r="Q392" s="232"/>
       <c r="R392" s="14" t="s">
         <v>16</v>
       </c>
@@ -22563,9 +22566,9 @@
       <c r="L426" s="67"/>
       <c r="M426" s="16"/>
       <c r="N426" s="16"/>
-      <c r="O426" s="230"/>
-      <c r="P426" s="230"/>
-      <c r="Q426" s="230"/>
+      <c r="O426" s="232"/>
+      <c r="P426" s="232"/>
+      <c r="Q426" s="232"/>
       <c r="R426" s="14"/>
       <c r="S426" s="46"/>
       <c r="T426" s="46" t="s">
@@ -22654,29 +22657,19 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="U34:W34"/>
-    <mergeCell ref="U130:W130"/>
-    <mergeCell ref="U98:W98"/>
-    <mergeCell ref="U65:W65"/>
-    <mergeCell ref="O65:R65"/>
-    <mergeCell ref="O98:R98"/>
-    <mergeCell ref="O66:Q66"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="O130:R130"/>
-    <mergeCell ref="O99:Q99"/>
-    <mergeCell ref="E65:N65"/>
-    <mergeCell ref="E98:N98"/>
-    <mergeCell ref="E130:N130"/>
-    <mergeCell ref="E34:N34"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="U163:W163"/>
-    <mergeCell ref="O164:Q164"/>
-    <mergeCell ref="O195:R195"/>
-    <mergeCell ref="U195:W195"/>
-    <mergeCell ref="O163:R163"/>
+    <mergeCell ref="U358:W358"/>
+    <mergeCell ref="U391:W391"/>
+    <mergeCell ref="O358:R358"/>
+    <mergeCell ref="E358:N358"/>
+    <mergeCell ref="E195:N195"/>
+    <mergeCell ref="U293:W293"/>
+    <mergeCell ref="U326:W326"/>
+    <mergeCell ref="U261:W261"/>
+    <mergeCell ref="E425:N425"/>
+    <mergeCell ref="O425:R425"/>
+    <mergeCell ref="O359:Q359"/>
+    <mergeCell ref="O391:R391"/>
+    <mergeCell ref="O228:Q228"/>
     <mergeCell ref="O426:Q426"/>
     <mergeCell ref="O131:Q131"/>
     <mergeCell ref="E261:N261"/>
@@ -22693,23 +22686,33 @@
     <mergeCell ref="O326:R326"/>
     <mergeCell ref="O294:Q294"/>
     <mergeCell ref="E163:N163"/>
-    <mergeCell ref="E425:N425"/>
-    <mergeCell ref="O425:R425"/>
-    <mergeCell ref="O359:Q359"/>
-    <mergeCell ref="O391:R391"/>
-    <mergeCell ref="O228:Q228"/>
-    <mergeCell ref="U358:W358"/>
-    <mergeCell ref="U391:W391"/>
-    <mergeCell ref="O358:R358"/>
-    <mergeCell ref="E358:N358"/>
-    <mergeCell ref="E195:N195"/>
-    <mergeCell ref="U293:W293"/>
-    <mergeCell ref="U326:W326"/>
-    <mergeCell ref="U261:W261"/>
+    <mergeCell ref="U163:W163"/>
+    <mergeCell ref="O164:Q164"/>
+    <mergeCell ref="O195:R195"/>
+    <mergeCell ref="U195:W195"/>
+    <mergeCell ref="O163:R163"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="O130:R130"/>
+    <mergeCell ref="O99:Q99"/>
+    <mergeCell ref="E65:N65"/>
+    <mergeCell ref="E98:N98"/>
+    <mergeCell ref="E130:N130"/>
+    <mergeCell ref="E34:N34"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="U34:W34"/>
+    <mergeCell ref="U130:W130"/>
+    <mergeCell ref="U98:W98"/>
+    <mergeCell ref="U65:W65"/>
+    <mergeCell ref="O65:R65"/>
+    <mergeCell ref="O98:R98"/>
+    <mergeCell ref="O66:Q66"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967294" verticalDpi="4294967294" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="landscape" horizontalDpi="4294967294" verticalDpi="4294967294" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="12" manualBreakCount="12">
     <brk id="33" max="16383" man="1"/>
@@ -24877,7 +24880,7 @@
       </c>
       <c r="E92">
         <f>COUNTIF(General!H$328:H$357,"S")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F92">
         <f>COUNTIF(General!I$328:I$357,"N")</f>
@@ -24885,7 +24888,7 @@
       </c>
       <c r="G92">
         <f>SUM(B92:F92)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -24935,7 +24938,7 @@
       </c>
       <c r="E94">
         <f>SUM(E92:E93)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F94">
         <f>SUM(F92:F93)</f>
@@ -24943,7 +24946,7 @@
       </c>
       <c r="G94">
         <f>SUM(B94:F94)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -25061,7 +25064,7 @@
       </c>
       <c r="E100">
         <f>E52+E56+E60+E64+E68+E72+E76+E80+E84+E92+E88+E96</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F100">
         <f>F52+F56+F60+F64+F68+F72+F76+F80+F84+F92+F88+F96</f>
@@ -25069,7 +25072,7 @@
       </c>
       <c r="G100">
         <f>G52+G56+G60+G64+G68+G72+G76+G80+G84+G92+G88+G95</f>
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -25119,7 +25122,7 @@
       </c>
       <c r="E102">
         <f t="shared" si="21"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F102">
         <f t="shared" si="21"/>
@@ -25127,7 +25130,7 @@
       </c>
       <c r="G102">
         <f t="shared" si="21"/>
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -25268,11 +25271,11 @@
       <c r="N2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="230" t="s">
+      <c r="O2" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="230"/>
-      <c r="Q2" s="230"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
       <c r="R2" s="14" t="s">
         <v>16</v>
       </c>
@@ -27724,11 +27727,11 @@
       <c r="N65" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="O65" s="230" t="s">
+      <c r="O65" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="P65" s="230"/>
-      <c r="Q65" s="230"/>
+      <c r="P65" s="232"/>
+      <c r="Q65" s="232"/>
       <c r="R65" s="14" t="s">
         <v>16</v>
       </c>

--- a/turnos/plan.xlsx
+++ b/turnos/plan.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3333" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3339" uniqueCount="304">
   <si>
     <t>Día</t>
   </si>
@@ -981,6 +981,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Ma M B</t>
+  </si>
+  <si>
+    <t>Talavera ya está en CCR</t>
   </si>
 </sst>
 </file>
@@ -18185,7 +18188,9 @@
       <c r="P325" s="45"/>
       <c r="Q325" s="45"/>
       <c r="R325" s="25"/>
-      <c r="S325" s="56"/>
+      <c r="S325" s="56" t="s">
+        <v>54</v>
+      </c>
       <c r="T325" s="25"/>
       <c r="U325" s="25"/>
       <c r="V325" s="25"/>
@@ -18336,7 +18341,9 @@
       <c r="Q328" s="45"/>
       <c r="R328" s="25"/>
       <c r="S328" s="25"/>
-      <c r="T328" s="25"/>
+      <c r="T328" s="25" t="s">
+        <v>54</v>
+      </c>
       <c r="U328" s="25"/>
       <c r="V328" s="25"/>
       <c r="W328" s="25"/>
@@ -18376,7 +18383,9 @@
       <c r="S329" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="T329" s="25"/>
+      <c r="T329" s="25" t="s">
+        <v>54</v>
+      </c>
       <c r="U329" s="25"/>
       <c r="V329" s="25"/>
       <c r="W329" s="25"/>
@@ -18725,7 +18734,9 @@
       <c r="Q336" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="R336" s="185"/>
+      <c r="R336" s="185" t="s">
+        <v>75</v>
+      </c>
       <c r="S336" s="25" t="s">
         <v>260</v>
       </c>
@@ -18765,9 +18776,7 @@
       </c>
       <c r="H337" s="25"/>
       <c r="I337" s="25"/>
-      <c r="J337" s="25" t="s">
-        <v>16</v>
-      </c>
+      <c r="J337" s="25"/>
       <c r="K337" s="25"/>
       <c r="L337" s="100"/>
       <c r="M337" s="25"/>
@@ -18793,7 +18802,9 @@
       <c r="W337" s="25"/>
       <c r="X337" s="202"/>
       <c r="Y337" s="25"/>
-      <c r="Z337" s="26"/>
+      <c r="Z337" s="26" t="s">
+        <v>303</v>
+      </c>
       <c r="AA337" s="26"/>
       <c r="AB337" s="26"/>
       <c r="AC337" s="82"/>
@@ -19068,7 +19079,9 @@
       <c r="O343" s="45"/>
       <c r="P343" s="45"/>
       <c r="Q343" s="45"/>
-      <c r="R343" s="25"/>
+      <c r="R343" s="185" t="s">
+        <v>75</v>
+      </c>
       <c r="S343" s="25"/>
       <c r="T343" s="25"/>
       <c r="U343" s="25"/>
@@ -19122,7 +19135,6 @@
       <c r="Q344" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="R344" s="185"/>
       <c r="S344" s="25"/>
       <c r="T344" s="25"/>
       <c r="U344" s="25"/>
@@ -19395,12 +19407,12 @@
         <v>9</v>
       </c>
       <c r="E350" s="25"/>
-      <c r="F350" s="25"/>
+      <c r="F350" s="25" t="s">
+        <v>9</v>
+      </c>
       <c r="G350" s="25"/>
       <c r="H350" s="25"/>
-      <c r="I350" s="25" t="s">
-        <v>9</v>
-      </c>
+      <c r="I350" s="25"/>
       <c r="J350" s="25"/>
       <c r="K350" s="25"/>
       <c r="L350" s="100"/>
@@ -19415,7 +19427,9 @@
       <c r="Q350" s="139" t="s">
         <v>294</v>
       </c>
-      <c r="R350" s="185"/>
+      <c r="R350" s="185" t="s">
+        <v>75</v>
+      </c>
       <c r="S350" s="25" t="s">
         <v>146</v>
       </c>
@@ -24872,7 +24886,7 @@
       </c>
       <c r="C92">
         <f>COUNTIF(General!F$328:F$357,"At")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92">
         <f>COUNTIF(General!G$328:G$357,"M")</f>
@@ -24888,7 +24902,7 @@
       </c>
       <c r="G92">
         <f>SUM(B92:F92)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -24930,7 +24944,7 @@
       </c>
       <c r="C94">
         <f>SUM(C92:C93)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94">
         <f>SUM(D92:D93)</f>
@@ -24946,7 +24960,7 @@
       </c>
       <c r="G94">
         <f>SUM(B94:F94)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -25056,7 +25070,7 @@
       </c>
       <c r="C100">
         <f>C52+C56+C60+C64+C68+C72+C76+C80+C84+C92+C88+C96</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D100">
         <f>D52+D56+D60+D64+D68+D72+D76+D80+D84+D92+D88+D96</f>
@@ -25072,7 +25086,7 @@
       </c>
       <c r="G100">
         <f>G52+G56+G60+G64+G68+G72+G76+G80+G84+G92+G88+G95</f>
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -25114,7 +25128,7 @@
       </c>
       <c r="C102">
         <f t="shared" si="21"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D102">
         <f t="shared" si="21"/>
@@ -25130,7 +25144,7 @@
       </c>
       <c r="G102">
         <f t="shared" si="21"/>
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="1:7">
